--- a/artfynd/A 50516-2023 artfynd.xlsx
+++ b/artfynd/A 50516-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>119009668</v>
       </c>
       <c r="B2" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -796,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119009964</v>
+        <v>119009669</v>
       </c>
       <c r="B3" t="n">
-        <v>57984</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570302</v>
+        <v>570169</v>
       </c>
       <c r="R3" t="n">
-        <v>6967287</v>
+        <v>6967256</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +860,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:33</t>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>övriga läten</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +910,7 @@
         <v>119009965</v>
       </c>
       <c r="B4" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1041,15 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119010687</v>
+        <v>119009966</v>
       </c>
       <c r="B5" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,16 +1064,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Flärkberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570092</v>
+        <v>570070</v>
       </c>
       <c r="R5" t="n">
-        <v>6967333</v>
+        <v>6967310</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,22 +1108,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>04:48</t>
+          <t>07:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>04:48</t>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>övr läte</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,15 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119009669</v>
+        <v>119010687</v>
       </c>
       <c r="B6" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570169</v>
+        <v>570092</v>
       </c>
       <c r="R6" t="n">
-        <v>6967256</v>
+        <v>6967333</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1231,27 +1224,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>övriga läten</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,6 +1263,117 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119009964</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Flärkberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570302</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6967287</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50516-2023 artfynd.xlsx
+++ b/artfynd/A 50516-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009668</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009669</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009965</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009966</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119010687</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,8 +1404,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119009964</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>